--- a/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
+++ b/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
@@ -234,12 +234,18 @@
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" sqref="A2:A30">
+      <formula1>ISNUMBER(A2)</formula1>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid salary" error="Salary must be between 0 and 1,000,000." promptTitle="Salary" prompt="Annual salary in USD." sqref="E2:E30">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G30">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F30">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G30">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
+++ b/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
@@ -235,17 +235,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" sqref="A2:A30">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A30">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid salary" error="Salary must be between 0 and 1,000,000." promptTitle="Salary" prompt="Annual salary in USD." sqref="E2:E30">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F30">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F30">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G30">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="G2:G30">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
+++ b/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
@@ -229,14 +229,30 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
+  <conditionalFormatting sqref="A2:A30">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B30">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C30">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A30">
+  <dataValidations count="6">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A30">
       <formula1>ISNUMBER(A2)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B30">
+      <formula1>LEN(TRIM(B2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C30">
+      <formula1>LEN(TRIM(C2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid salary" error="Salary must be between 0 and 1,000,000." promptTitle="Salary" prompt="Annual salary in USD." sqref="E2:E30">
       <formula1>0</formula1>

--- a/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
+++ b/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -266,4 +266,18 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Id"/>
+    <column index="2" property="Name"/>
+    <column index="3" property="Email"/>
+    <column index="4" property="HireDate"/>
+    <column index="5" property="Salary"/>
+    <column index="6" property="IsActive"/>
+    <column index="7" property="Status"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
+++ b/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
@@ -132,7 +132,7 @@
         <v>75000</v>
       </c>
       <c r="F2" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -161,7 +161,7 @@
         <v>120000</v>
       </c>
       <c r="F3" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -190,7 +190,7 @@
         <v>45000</v>
       </c>
       <c r="F4" s="2" t="b">
-        <v>false</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -219,7 +219,7 @@
         <v>95000</v>
       </c>
       <c r="F5" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>

--- a/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
+++ b/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
@@ -68,7 +68,7 @@
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>

--- a/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
+++ b/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
@@ -65,11 +65,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>

--- a/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
+++ b/src/Excelsior.Tests/ValidationTests.ShortcutMethods.verified.xlsx
@@ -65,11 +65,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
